--- a/Pratice sheet.xlsx
+++ b/Pratice sheet.xlsx
@@ -8,12 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\amulm\OneDrive\Desktop\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69A84F9B-E506-4D78-9BB1-9D53E3B12C4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6FE46BA-C5A9-41B9-A125-43DA8E6A8606}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{5302BE36-0E86-45E4-9EEE-6687E68765EF}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" activeTab="2" xr2:uid="{5302BE36-0E86-45E4-9EEE-6687E68765EF}"/>
   </bookViews>
   <sheets>
     <sheet name="Pratice sheet" sheetId="1" r:id="rId1"/>
+    <sheet name="SUM PRTATICE SHEET" sheetId="2" r:id="rId2"/>
+    <sheet name="CountIF pratice sheet" sheetId="3" r:id="rId3"/>
+    <sheet name="Countifs Pratice Sheet" sheetId="4" r:id="rId4"/>
+    <sheet name="Combination of everything" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="68">
   <si>
     <t>A (Name)</t>
   </si>
@@ -72,6 +76,9 @@
   </si>
   <si>
     <t>Amit</t>
+  </si>
+  <si>
+    <t>(blank)</t>
   </si>
   <si>
     <t>Neha</t>
@@ -167,12 +174,123 @@
   <si>
     <t>COUNTA is used give me 7 because BLANK CELL does not count the EMPTY CELL</t>
   </si>
+  <si>
+    <t>B (Department)</t>
+  </si>
+  <si>
+    <t>C (Region)</t>
+  </si>
+  <si>
+    <t>North</t>
+  </si>
+  <si>
+    <t>South</t>
+  </si>
+  <si>
+    <t>West</t>
+  </si>
+  <si>
+    <t>What is the total salary of all employees?</t>
+  </si>
+  <si>
+    <t>What is the total salary of the first 4 employees only?</t>
+  </si>
+  <si>
+    <t>What is the total salary of employees from row 3 to row 6?</t>
+  </si>
+  <si>
+    <t>Total salary of IT department</t>
+  </si>
+  <si>
+    <t>Total salary of HR department</t>
+  </si>
+  <si>
+    <t>Total salary of employees in South region</t>
+  </si>
+  <si>
+    <t>Total salary greater than 50,000</t>
+  </si>
+  <si>
+    <t>Total salary less than 48,000</t>
+  </si>
+  <si>
+    <t>Total salary equal to 49,000</t>
+  </si>
+  <si>
+    <t>What will happen if you use:</t>
+  </si>
+  <si>
+    <t>IT doesn’t print because SUM only adds the numbers</t>
+  </si>
+  <si>
+    <t>Count employees in IT department</t>
+  </si>
+  <si>
+    <t>Count employees in HR department</t>
+  </si>
+  <si>
+    <t>Count employees in South region</t>
+  </si>
+  <si>
+    <t>1. Count employees in Sales department</t>
+  </si>
+  <si>
+    <t>Count salaries greater than 50,000</t>
+  </si>
+  <si>
+    <t>Count salaries less than 48,000</t>
+  </si>
+  <si>
+    <t>Count salaries equal to 49,000</t>
+  </si>
+  <si>
+    <t>Count salaries greater than or equal to 51,000</t>
+  </si>
+  <si>
+    <t>B (Dept)</t>
+  </si>
+  <si>
+    <t>E (Experience Years)</t>
+  </si>
+  <si>
+    <t>D (Sales)</t>
+  </si>
+  <si>
+    <t>E (Month)</t>
+  </si>
+  <si>
+    <t>Jan</t>
+  </si>
+  <si>
+    <t>Feb</t>
+  </si>
+  <si>
+    <t>Rohan</t>
+  </si>
+  <si>
+    <t>Divya</t>
+  </si>
+  <si>
+    <t>PART 1 — COUNT</t>
+  </si>
+  <si>
+    <t>PART 2-COUNTIF</t>
+  </si>
+  <si>
+    <t>PART 3 SUM</t>
+  </si>
+  <si>
+    <t>PART 4 SUMIF</t>
+  </si>
+  <si>
+    <t>Thinking Question</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -192,6 +310,29 @@
       <sz val="10"/>
       <color theme="1"/>
       <name val="Arial Unicode MS"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -214,13 +355,29 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -643,7 +800,7 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7" s="2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" s="2">
         <v>26</v>
@@ -657,7 +814,7 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B8" s="2">
         <v>23</v>
@@ -669,7 +826,7 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B9" s="2">
         <v>24</v>
@@ -683,7 +840,7 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E13">
         <f>COUNT(B2:B9)</f>
@@ -692,7 +849,7 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E15">
         <f>COUNTA(D2:D9)</f>
@@ -701,7 +858,7 @@
     </row>
     <row r="18" spans="1:7">
       <c r="A18" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G18">
         <f>COUNT(B2:B9)</f>
@@ -710,12 +867,12 @@
     </row>
     <row r="21" spans="1:7">
       <c r="A21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="22" spans="1:7">
       <c r="A22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E22">
         <f>COUNTA(A2:A9)</f>
@@ -724,7 +881,7 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E24">
         <f>COUNTA(C2:C9)</f>
@@ -733,7 +890,7 @@
     </row>
     <row r="26" spans="1:7">
       <c r="A26" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G26">
         <f>COUNTA(D2:D9)</f>
@@ -742,46 +899,1018 @@
     </row>
     <row r="27" spans="1:7">
       <c r="A27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28" spans="1:7">
       <c r="A28" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F28">
         <f>COUNT(A2:A9)</f>
         <v>0</v>
       </c>
       <c r="G28" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="F30">
         <f>COUNTA(B2:B9)</f>
         <v>7</v>
       </c>
       <c r="G30" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
     <row r="33" spans="1:1">
       <c r="A33" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
     <row r="35" spans="1:1">
       <c r="A35" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="36" spans="1:1">
       <c r="A36" t="s">
-        <v>29</v>
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8349BE0F-B51B-4BEB-B86F-081B02BFDA53}">
+  <dimension ref="A1:D24"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="15.54296875" customWidth="1"/>
+    <col min="2" max="2" width="20.26953125" customWidth="1"/>
+    <col min="3" max="3" width="19.36328125" customWidth="1"/>
+    <col min="4" max="4" width="26.26953125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="2">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="2">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="2">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="2">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2">
+        <v>51000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="2">
+        <v>47000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="2">
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="2">
+        <v>53000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C12">
+        <f>SUM(D2:D9)</f>
+        <v>395000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13">
+        <f>SUM(D2:D5)</f>
+        <v>195000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>38</v>
+      </c>
+      <c r="D14">
+        <f>SUM(D4:D7)</f>
+        <v>198000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" t="s">
+        <v>39</v>
+      </c>
+      <c r="C16">
+        <f>SUMIF(B2:B9,"IT",D2:D9)</f>
+        <v>206000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>40</v>
+      </c>
+      <c r="C17">
+        <f>SUMIF(B2:B9,"HR",D2:D9)</f>
+        <v>92000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>41</v>
+      </c>
+      <c r="C18">
+        <f>SUMIF(C2:C9,"South",D2:D9)</f>
+        <v>145000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20">
+        <f>SUMIF(D2:D9,"&gt;50000")</f>
+        <v>156000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="A21" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21">
+        <f>SUMIF(D2:D9,"&lt;480000")</f>
+        <v>395000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
+      <c r="A22" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22">
+        <f>SUMIF(D2:D9,"=490000")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
+      <c r="A24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D96BE4B7-0FD9-4AB8-AB84-E96E4D93CC00}">
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr defaultRowHeight="16"/>
+  <cols>
+    <col min="1" max="1" width="16.90625" customWidth="1"/>
+    <col min="2" max="2" width="19.26953125" style="7" customWidth="1"/>
+    <col min="3" max="3" width="13.08984375" customWidth="1"/>
+    <col min="4" max="4" width="17.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" s="5" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="2">
+        <v>50000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="2">
+        <v>45000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="2">
+        <v>52000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="2">
+        <v>48000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2">
+        <v>51000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="2">
+        <v>47000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="2">
+        <v>49000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="2">
+        <v>53000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12">
+        <f>COUNTIF(B2:B9,"IT")</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
+        <v>48</v>
+      </c>
+      <c r="C13">
+        <f>COUNTIF(B2:B9,"HR")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
+        <v>49</v>
+      </c>
+      <c r="C14">
+        <f>COUNTIF(C2:C9,"south")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="8" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15">
+        <f>COUNTIF(B2:B9,"Sales")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
+        <v>51</v>
+      </c>
+      <c r="C17">
+        <f>COUNTIF(D2:D9,"&gt;50000")</f>
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
+      <c r="A18" t="s">
+        <v>52</v>
+      </c>
+      <c r="C18">
+        <f>COUNTIF(D2:D9,"&lt;48000")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3">
+      <c r="A19" t="s">
+        <v>53</v>
+      </c>
+      <c r="C19">
+        <f>COUNTIF(D2:D9,"49000")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
+      <c r="A20" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20">
+        <f>COUNTIF(D2:D9,"&gt;=510000")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
+      <c r="C21">
+        <f>COUNTIF(D2:D9,"50000")</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
+      <c r="B23" s="7">
+        <f>COUNTIF(D2:D9,"&gt;=50000")</f>
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95E389CA-178D-4DBE-87DC-EA801C4BE29E}">
+  <dimension ref="A1:E18"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="12.1796875" customWidth="1"/>
+    <col min="2" max="2" width="13.7265625" customWidth="1"/>
+    <col min="3" max="3" width="12.08984375" customWidth="1"/>
+    <col min="4" max="4" width="12.54296875" customWidth="1"/>
+    <col min="5" max="5" width="13.1796875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5" ht="26">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="2">
+        <v>50000</v>
+      </c>
+      <c r="E2" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="2">
+        <v>45000</v>
+      </c>
+      <c r="E3" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="2">
+        <v>52000</v>
+      </c>
+      <c r="E4" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="2">
+        <v>48000</v>
+      </c>
+      <c r="E5" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2">
+        <v>51000</v>
+      </c>
+      <c r="E6" s="2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="2">
+        <v>47000</v>
+      </c>
+      <c r="E7" s="2">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="2">
+        <v>49000</v>
+      </c>
+      <c r="E8" s="2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="2">
+        <v>53000</v>
+      </c>
+      <c r="E9" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11">
+        <f>COUNTIFS(B2:B9,"IT",C2:C9,"North")</f>
+        <v>2</v>
+      </c>
+      <c r="B11">
+        <f>COUNTIFS(B2:B9,"IT",D2:D9,"&gt;50000")</f>
+        <v>3</v>
+      </c>
+      <c r="C11">
+        <f>COUNTIFS(B2:B9,"IT",D2:D9,"&gt;=510000",E2:E9,"&gt;=4")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="A12">
+        <f>COUNTIFS(B2:B9,"HR",C2:C9,"North")</f>
+        <v>1</v>
+      </c>
+      <c r="B12">
+        <f>COUNTIFS(B2:B9,"HR",E2:E9,"&gt;=5")</f>
+        <v>1</v>
+      </c>
+      <c r="C12">
+        <f>COUNTIFS(B2:B9,"Marketing", C2:C9,"North")</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13">
+        <f>COUNTIFS(B2:B9,"Sales",C2:C9,"South")</f>
+        <v>1</v>
+      </c>
+      <c r="B13">
+        <f>COUNTIFS(C2:C9,"South",D2:D9,"&lt;50000")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14">
+        <f>COUNTIFS(B2:B9,"IT",C2:C9,"West")</f>
+        <v>1</v>
+      </c>
+      <c r="B14">
+        <f>COUNTIFS(C2:C9,"North",E2:E9,"&gt;=3")</f>
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <f>COUNTIFS(C2:C9,"North",D2:D9,"&gt;=50000",E2:E9,"&gt;3")</f>
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B510A31-CC88-41DF-9C70-4D6A2385A2ED}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="17.36328125" customWidth="1"/>
+    <col min="2" max="2" width="17.7265625" customWidth="1"/>
+    <col min="3" max="3" width="14.81640625" customWidth="1"/>
+    <col min="4" max="4" width="16.26953125" customWidth="1"/>
+    <col min="5" max="5" width="15" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="29">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D2" s="2">
+        <v>5000</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D3" s="2">
+        <v>7000</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D4" s="2">
+        <v>8000</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D5" s="2">
+        <v>6000</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D6" s="2">
+        <v>9000</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="2">
+        <v>4000</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="2">
+        <v>7500</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D9" s="2">
+        <v>6500</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D10" s="2">
+        <v>7200</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="29">
+      <c r="A14" t="s">
+        <v>63</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" t="s">
+        <v>66</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15">
+        <f>COUNT(D2:D11)</f>
+        <v>9</v>
+      </c>
+      <c r="B15">
+        <f>COUNTIF(B2:B11,"IT")</f>
+        <v>4</v>
+      </c>
+      <c r="C15">
+        <f>SUM(D2:D11)</f>
+        <v>60200</v>
+      </c>
+      <c r="D15">
+        <f>SUMIF(B2:B11,"IT",D2:D11)</f>
+        <v>28500</v>
+      </c>
+      <c r="E15">
+        <f>COUNT(A2:A11)</f>
+        <v>0</v>
+      </c>
+      <c r="F15">
+        <f>SUM(B2:B11)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16">
+        <f>COUNT(A2:A11)</f>
+        <v>0</v>
+      </c>
+      <c r="B16">
+        <f>COUNTIF(C2:C11,"South")</f>
+        <v>3</v>
+      </c>
+      <c r="C16">
+        <f>SUM(D3:D6)</f>
+        <v>30000</v>
+      </c>
+      <c r="D16">
+        <f>SUMIF(C2:C11,"South",D2:D11)</f>
+        <v>23500</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17">
+        <f>COUNT(A2:A11)</f>
+        <v>0</v>
+      </c>
+      <c r="B17">
+        <f>COUNTIF(D2:D11,"&gt;7000")</f>
+        <v>4</v>
+      </c>
+      <c r="D17">
+        <f>SUMIF(E2:E11,"Jan",D2:D11)</f>
+        <v>32000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="B18">
+        <f>COUNTIF(E2:E11,"Jan")</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="D20">
+        <f>SUMIF(D2:D11,"&gt;=6000")</f>
+        <v>51200</v>
       </c>
     </row>
   </sheetData>
